--- a/data/trans_orig/IP16B06-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/IP16B06-Provincia-trans_orig.xlsx
@@ -6112,7 +6112,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>634</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>2570</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6230,7 +6230,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2947</t>
+          <t>2313</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6245,7 +6245,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>78,5%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6300,7 +6300,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>54,22%</t>
         </is>
       </c>
     </row>
